--- a/ingestion/coa_track/letta-imb-coas/exports/PP_Open_Reconciliation_Items.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_Open_Reconciliation_Items.xlsx
@@ -970,7 +970,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>ППК25176, 626/1127/25</t>
+          <t>ППК25176, 3177/2025</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>n/a, ППК26115</t>
+          <t>ППК26115, n/a</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>n/a, ППК26117</t>
+          <t>ППК26117, n/a</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">

--- a/ingestion/coa_track/letta-imb-coas/exports/PP_Open_Reconciliation_Items.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_Open_Reconciliation_Items.xlsx
@@ -970,7 +970,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>ППК25176, 3177/2025</t>
+          <t>3177/2025, 626/1127/25</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>n/a, ППК26127</t>
+          <t>ППК26127, n/a</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>ППК26115, n/a</t>
+          <t>n/a, ППК26115</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>n/a, ППК26118</t>
+          <t>ППК26118, n/a</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>n/a, ППК26119</t>
+          <t>ППК26119, n/a</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">

--- a/ingestion/coa_track/letta-imb-coas/exports/PP_Open_Reconciliation_Items.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_Open_Reconciliation_Items.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Open Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Open Items'!$A$5:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Open Items'!$A$5:$H$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>3177/2025, 626/1127/25</t>
+          <t>626/1127/25, 3177/2025</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>ППК26127, n/a</t>
+          <t>n/a, ППК26127</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>n/a, ППК26128</t>
+          <t>ППК26128, n/a</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>ППК26117, n/a</t>
+          <t>n/a, ППК26117</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>ППК26118, n/a</t>
+          <t>n/a, ППК26118</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>ППК26119, n/a</t>
+          <t>n/a, ППК26119</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>CJ052501/1</t>
+          <t>CLE072501</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Clemosa</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Clemosa a bud</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>CJ052501/2</t>
+          <t>GG012601</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>GG4</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>CJ072501</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>GG4</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>CJ082501/1</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>GG4</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>CJ082501/2</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>CJ092501</t>
+          <t>JD012601</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>CJ1024</t>
+          <t>JD012603/2</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>CLE072501</t>
+          <t>JD012603/2V</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Clemosa</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr"/>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>GG012601</t>
+          <t>JD112501</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>GG4</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr"/>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>SJ092501</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>GG4</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>GG112501</t>
+          <t>SJ102501</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>GG4</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr"/>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>JD012601</t>
+          <t>WC072501</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>JD012603/2</t>
+          <t>WC082501</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr"/>
@@ -1765,33 +1765,37 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>JD012603/2V</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Strain name spelled differently</t>
+          <t>Released THC % differs by 0.08</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>20.47 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr"/>
+          <t>20.39 %</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>In-house GC cross-check NGP/QCG/SOP-024</t>
+        </is>
+      </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>Two spellings of one cultivar. The certificate spelling is what an outsourced lab printed; the sheet spelling is the house name. A CoQ should carry one of them consistently.</t>
+          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
         </is>
       </c>
     </row>
@@ -1801,33 +1805,37 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>JD112501</t>
+          <t>BSS1024</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Strain name spelled differently</t>
+          <t>Released THC % differs by 0.03</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>21.00 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="inlineStr"/>
+          <t>21.03 % / 25.01 %</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>ППК25051</t>
+        </is>
+      </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Two spellings of one cultivar. The certificate spelling is what an outsourced lab printed; the sheet spelling is the house name. A CoQ should carry one of them consistently.</t>
+          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
         </is>
       </c>
     </row>
@@ -1837,33 +1845,37 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>SJ092501</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Strain name spelled differently</t>
+          <t>Released THC % differs by 2.04</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>15.63 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr"/>
+          <t>17.67 %</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>197-6-К/26</t>
+        </is>
+      </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>Two spellings of one cultivar. The certificate spelling is what an outsourced lab printed; the sheet spelling is the house name. A CoQ should carry one of them consistently.</t>
+          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
         </is>
       </c>
     </row>
@@ -1873,33 +1885,37 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SJ102501</t>
+          <t>CJ052501/2</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Strain name spelled differently</t>
+          <t>Released THC % differs by 0.44</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>14.49 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="inlineStr"/>
+          <t>14.93 %</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>ППК25281</t>
+        </is>
+      </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Two spellings of one cultivar. The certificate spelling is what an outsourced lab printed; the sheet spelling is the house name. A CoQ should carry one of them consistently.</t>
+          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
         </is>
       </c>
     </row>
@@ -1909,33 +1925,37 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>FB012602</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Strain name spelled differently</t>
+          <t>Released THC % differs by 0.91</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>19.77 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr"/>
+          <t>18.86 %</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>197-7-К/26</t>
+        </is>
+      </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>Two spellings of one cultivar. The certificate spelling is what an outsourced lab printed; the sheet spelling is the house name. A CoQ should carry one of them consistently.</t>
+          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
         </is>
       </c>
     </row>
@@ -1945,33 +1965,37 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>WC072501</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Strain name spelled differently</t>
+          <t>Released THC % differs by 6.18</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>Wedding Crusher</t>
+          <t>14.65 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr"/>
+          <t>20.83 %</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>ППК26112</t>
+        </is>
+      </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Two spellings of one cultivar. The certificate spelling is what an outsourced lab printed; the sheet spelling is the house name. A CoQ should carry one of them consistently.</t>
+          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
         </is>
       </c>
     </row>
@@ -1981,33 +2005,37 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>WC082501</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Strain name spelled differently</t>
+          <t>Released THC % differs by 2.69</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Wedding Crusher</t>
+          <t>15.60 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr"/>
+          <t>18.29 %</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>ППК26110</t>
+        </is>
+      </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>Two spellings of one cultivar. The certificate spelling is what an outsourced lab printed; the sheet spelling is the house name. A CoQ should carry one of them consistently.</t>
+          <t>The Quantities table marks this batch 'anal.ong.' — analysis ongoing — so the sheet figure was entered before the certificate arrived. The certificate figure is the later one.</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2050,32 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>BSS052501</t>
+          <t>GG012603</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Released THC % differs by 0.08</t>
+          <t>Released THC % differs by 1.11</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>20.47 % (Tranches Overview)</t>
+          <t>15.59 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>20.39 %</t>
+          <t>16.70 % / 17.59 %</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>In-house GC cross-check NGP/QCG/SOP-024</t>
+          <t>197-8-К/26</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
+          <t>The Quantities table marks this batch 'anal.ong.' — analysis ongoing — so the sheet figure was entered before the certificate arrived. The certificate figure is the later one.</t>
         </is>
       </c>
     </row>
@@ -2062,27 +2090,27 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>BSS1024</t>
+          <t>GG1024_01</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Released THC % differs by 0.03</t>
+          <t>Released THC % differs by 0.22</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>21.00 % (Tranches Overview)</t>
+          <t>17.00 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>21.03 % / 25.01 %</t>
+          <t>17.22 % / 18.67 %</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>ППК25051</t>
+          <t>ППК25104</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
@@ -2102,27 +2130,27 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>GP062501</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Released THC % differs by 2.04</t>
+          <t>Released THC % differs by 2.00</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>15.63 % (Tranches Overview)</t>
+          <t>22.89 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>17.67 %</t>
+          <t>24.89 %</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>197-6-К/26</t>
+          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -2142,32 +2170,32 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>CJ052501/2</t>
+          <t>GP0824_01</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Released THC % differs by 0.44</t>
+          <t>Released THC % differs by 0.79</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>14.49 % (Tranches Overview)</t>
+          <t>20.00 % (List of COAs)</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>14.93 %</t>
+          <t>20.79 %</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>ППК25281</t>
+          <t>ППК25105</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
+          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
         </is>
       </c>
     </row>
@@ -2182,32 +2210,32 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>FB012602</t>
+          <t>J31112501</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Released THC % differs by 0.91</t>
+          <t>Released THC % differs by 0.27</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>19.77 % (Tranches Overview)</t>
+          <t>25.00 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>18.86 %</t>
+          <t>20.21 % / 25.27 %</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>197-7-К/26</t>
+          <t>051-5-K/26</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
+          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
         </is>
       </c>
     </row>
@@ -2222,27 +2250,27 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Released THC % differs by 6.18</t>
+          <t>Released THC % differs by 0.07</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>14.65 % (Tranches Overview)</t>
+          <t>21.77 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>20.83 %</t>
+          <t>19.84 % / 21.84 %</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>ППК26112</t>
+          <t>100-3-К/26</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -2262,27 +2290,27 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>FB012603V</t>
+          <t>JD012603/2</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Released THC % differs by 2.69</t>
+          <t>Released THC % differs by 7.24</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>15.60 % (Tranches Overview)</t>
+          <t>13.30 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>18.29 %</t>
+          <t>20.54 %</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>ППК26110</t>
+          <t>ППК26113</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -2302,27 +2330,27 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>GG012603</t>
+          <t>JD012603/2V</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Released THC % differs by 1.11</t>
+          <t>Released THC % differs by 0.19</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>15.59 % (Tranches Overview)</t>
+          <t>14.97 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>16.70 % / 17.59 %</t>
+          <t>15.16 %</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>197-8-К/26</t>
+          <t>ППК26111</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -2342,32 +2370,32 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>GG1024_01</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Released THC % differs by 0.22</t>
+          <t>Released THC % differs by 0.36</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>17.00 % (Tranches Overview)</t>
+          <t>17.40 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>17.22 % / 18.67 %</t>
+          <t>17.04 %</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>ППК25104</t>
+          <t>051-4-K/26</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
+          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
         </is>
       </c>
     </row>
@@ -2382,32 +2410,32 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Released THC % differs by 2.00</t>
+          <t>Released THC % differs by 2.91</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>22.89 % (Tranches Overview)</t>
+          <t>11.00 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>24.89 %</t>
+          <t>7.91 % / 8.09 %</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>In-house HPLC cross-check NPCCC/SCP-02, NGP/QCG/SOP-024</t>
+          <t>100-4-К/26</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
+          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
         </is>
       </c>
     </row>
@@ -2422,27 +2450,27 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>GP0824_01</t>
+          <t>PM112501</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Released THC % differs by 0.79</t>
+          <t>Released THC % differs by 0.33</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>20.00 % (List of COAs)</t>
+          <t>13.00 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>20.79 %</t>
+          <t>13.33 %</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>ППК25105</t>
+          <t>ППК26030</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -2462,27 +2490,27 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>J31112501</t>
+          <t>SCR012603</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Released THC % differs by 0.27</t>
+          <t>Released THC % differs by 0.84</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>25.00 % (Tranches Overview)</t>
+          <t>17.00 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>20.21 % / 25.27 %</t>
+          <t>17.84 %</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>051-5-K/26</t>
+          <t>197-21-К/26</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -2502,32 +2530,32 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Released THC % differs by 0.07</t>
+          <t>Released THC % differs by 5.92</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>21.77 % (Tranches Overview)</t>
+          <t>16.00 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>19.84 % / 21.84 %</t>
+          <t>21.92 %</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>100-3-К/26</t>
+          <t>ППК26116</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
+          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
         </is>
       </c>
     </row>
@@ -2542,317 +2570,37 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>JD012603/2</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Released THC % differs by 7.24</t>
+          <t>Released THC % differs by 0.20</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>13.30 % (Tranches Overview)</t>
+          <t>9.00 % (Tranches Overview)</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>20.54 %</t>
+          <t>9.20 %</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>ППК26113</t>
+          <t>051-2-K/26</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>The Quantities table marks this batch 'anal.ong.' — analysis ongoing — so the sheet figure was entered before the certificate arrived. The certificate figure is the later one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>JD012603/2V</t>
-        </is>
-      </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>Released THC % differs by 0.19</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>14.97 % (Tranches Overview)</t>
-        </is>
-      </c>
-      <c r="F59" s="13" t="inlineStr">
-        <is>
-          <t>15.16 %</t>
-        </is>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>ППК26111</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="inlineStr">
-        <is>
-          <t>The Quantities table marks this batch 'anal.ong.' — analysis ongoing — so the sheet figure was entered before the certificate arrived. The certificate figure is the later one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>KC102501</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>Released THC % differs by 0.36</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>17.40 % (Tranches Overview)</t>
-        </is>
-      </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>17.04 %</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>051-4-K/26</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>Both sides are precise and they disagree. Worth checking which certificate was used to release the batch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr">
-        <is>
-          <t>OPM122501</t>
-        </is>
-      </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>Released THC % differs by 2.91</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>11.00 % (Tranches Overview)</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="inlineStr">
-        <is>
-          <t>7.91 % / 8.09 %</t>
-        </is>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>100-4-К/26</t>
-        </is>
-      </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
           <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>PM112501</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>Released THC % differs by 0.33</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>13.00 % (Tranches Overview)</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>13.33 %</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>ППК26030</t>
-        </is>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="inlineStr">
-        <is>
-          <t>SCR012603</t>
-        </is>
-      </c>
-      <c r="D63" s="13" t="inlineStr">
-        <is>
-          <t>Released THC % differs by 0.84</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>17.00 % (Tranches Overview)</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="inlineStr">
-        <is>
-          <t>17.84 %</t>
-        </is>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>197-21-К/26</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>Released THC % differs by 5.92</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>16.00 % (Tranches Overview)</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>21.92 %</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>ППК26116</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>SJ112501</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="inlineStr">
-        <is>
-          <t>Released THC % differs by 0.20</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>9.00 % (Tranches Overview)</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="inlineStr">
-        <is>
-          <t>9.20 %</t>
-        </is>
-      </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>051-2-K/26</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>The sheet figure is a whole number while the certificate carries two decimals, which reads as a provisional entry rather than a transcription.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:H65"/>
+  <autoFilter ref="A5:H58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ingestion/coa_track/letta-imb-coas/exports/PP_Open_Reconciliation_Items.xlsx
+++ b/ingestion/coa_track/letta-imb-coas/exports/PP_Open_Reconciliation_Items.xlsx
@@ -970,7 +970,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>626/1127/25, 3177/2025</t>
+          <t>ППК25176, 626/1127/25</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>ППК26128, n/a</t>
+          <t>n/a, ППК26128</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>n/a, ППК26117</t>
+          <t>ППК26117, n/a</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
